--- a/sample_data/test_output_audit.xlsx
+++ b/sample_data/test_output_audit.xlsx
@@ -440,7 +440,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-14 01:12:00</t>
+          <t>2026-08-16 23:37:49</t>
         </is>
       </c>
     </row>
@@ -544,13 +544,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>96.2</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="C10" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D10" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E10" t="n">
         <v>1</v>
@@ -571,10 +571,10 @@
         <v>100</v>
       </c>
       <c r="C11" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -648,9 +648,9 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="31" customWidth="1" min="2" max="2"/>
+    <col width="41" customWidth="1" min="2" max="2"/>
     <col width="38" customWidth="1" min="3" max="3"/>
-    <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="73" customWidth="1" min="7" max="7"/>
@@ -711,7 +711,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>25.0mm x 60.0mm</t>
+          <t>60.0mm x 25.0mm</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -721,12 +721,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>CRITICAL</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Layout page dimensions match artwork physical die cut specifications.</t>
+          <t>Tag dimensions match signed artwork specification.</t>
         </is>
       </c>
     </row>
@@ -775,7 +775,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Brand Logo</t>
+          <t>Brand logo</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Found: 'LOVESKIN APPAREL'</t>
+          <t>Found: 'LoveSkin'</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -812,17 +812,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Brand Logo (Font)</t>
+          <t>Brand logo (Placement)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Helvetica-Bold 7.5pt</t>
+          <t>Inside safe print zone</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Helvetica-Bold 7.5pt</t>
+          <t>X: 3.0mm, Y: 5.98mm (W:12.55mm, H:3.89mm)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -832,12 +832,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Font family and size match artwork field specification.</t>
+          <t>Coordinates are within approved tolerance.</t>
         </is>
       </c>
     </row>
@@ -849,32 +849,32 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Brand Logo (Placement)</t>
+          <t>Size (Label)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Within safe margin (X: 1.0–24.0mm)</t>
+          <t>Present</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>X: -0.95mm, Y: 4.17mm</t>
+          <t>Found: 'Taglia / Size: S'</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Field is placed too close to the edge (-0.95mm) exceeding tolerance.</t>
+          <t>Field is present on the layout.</t>
         </is>
       </c>
     </row>
@@ -886,17 +886,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>RFID Logo / Text</t>
+          <t>Size (Label) (Font)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Present</t>
+          <t>Arial 5.0pt</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Found: '[((o))] RFID'</t>
+          <t>Helvetica 5.0pt</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -906,12 +906,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Field is present on the layout.</t>
+          <t>Font family and size match artwork field specification.</t>
         </is>
       </c>
     </row>
@@ -923,17 +923,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>RFID Logo / Text (Font)</t>
+          <t>Size (Label) (Placement)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Helvetica-Bold 6.0pt</t>
+          <t>Inside safe print zone</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Helvetica-Bold 6.0pt</t>
+          <t>X: 3.0mm, Y: 12.1mm (W:11.86mm, H:2.42mm)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -943,12 +943,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Font family and size match artwork field specification.</t>
+          <t>Coordinates are within approved tolerance.</t>
         </is>
       </c>
     </row>
@@ -960,17 +960,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>RFID Logo / Text (Placement)</t>
+          <t>Article number (Label)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Inside safe print zone</t>
+          <t>Present</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>X: 2.0mm, Y: 9.74mm (W:11.05mm, H:2.91mm)</t>
+          <t>Found: 'Articolo / Article: Z5E213TS'</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -985,7 +985,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Coordinates are within approved tolerance.</t>
+          <t>Field is present on the layout.</t>
         </is>
       </c>
     </row>
@@ -997,17 +997,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Article Number</t>
+          <t>Article number (Label) (Font)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Present</t>
+          <t>Arial 5.0pt</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Found: 'Article: 1000341139-PT'</t>
+          <t>Helvetica 5.0pt</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1017,12 +1017,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Field is present on the layout.</t>
+          <t>Font family and size match artwork field specification.</t>
         </is>
       </c>
     </row>
@@ -1034,17 +1034,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Article Number (Font)</t>
+          <t>Article number (Label) (Placement)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Helvetica 5.2pt</t>
+          <t>Inside safe print zone</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Helvetica 5.2pt</t>
+          <t>X: 3.0mm, Y: 15.6mm (W:21.66mm, H:2.42mm)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1054,12 +1054,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Font family and size match artwork field specification.</t>
+          <t>Coordinates are within approved tolerance.</t>
         </is>
       </c>
     </row>
@@ -1071,17 +1071,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Article Number (Placement)</t>
+          <t>Color (Label)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Inside safe print zone</t>
+          <t>Present</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>X: 2.0mm, Y: 15.03mm (W:19.27mm, H:2.52mm)</t>
+          <t>Found: 'Colore / Color: Nero'</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Coordinates are within approved tolerance.</t>
+          <t>Field is present on the layout.</t>
         </is>
       </c>
     </row>
@@ -1108,17 +1108,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Size Label</t>
+          <t>Color (Label) (Font)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Present</t>
+          <t>Arial 5.0pt</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Found: 'Size: M'</t>
+          <t>Helvetica 5.0pt</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1128,12 +1128,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Field is present on the layout.</t>
+          <t>Font family and size match artwork field specification.</t>
         </is>
       </c>
     </row>
@@ -1145,17 +1145,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Size Label (Font)</t>
+          <t>Color (Label) (Placement)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Helvetica 5.2pt</t>
+          <t>Inside safe print zone</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Helvetica 5.2pt</t>
+          <t>X: 3.0mm, Y: 19.1mm (W:15.68mm, H:2.42mm)</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Font family and size match artwork field specification.</t>
+          <t>Coordinates are within approved tolerance.</t>
         </is>
       </c>
     </row>
@@ -1182,17 +1182,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Size Label (Placement)</t>
+          <t>RFID Logo</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Inside safe print zone</t>
+          <t>Present</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>X: 2.0mm, Y: 19.03mm (W:6.12mm, H:2.52mm)</t>
+          <t>Found: '[RFID]'</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1207,7 +1207,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Coordinates are within approved tolerance.</t>
+          <t>Field is present on the layout.</t>
         </is>
       </c>
     </row>
@@ -1219,17 +1219,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Color Name</t>
+          <t>RFID Logo (Placement)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Present</t>
+          <t>Inside safe print zone</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Found: 'Color: Midnight Navy'</t>
+          <t>X: 3.0mm, Y: 22.11mm (W:5.29mm, H:2.43mm)</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Field is present on the layout.</t>
+          <t>Coordinates are within approved tolerance.</t>
         </is>
       </c>
     </row>
@@ -1256,17 +1256,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Color Name (Font)</t>
+          <t>Size (max 12 digits)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Helvetica 5.2pt</t>
+          <t>Present</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Helvetica 5.2pt</t>
+          <t>Found: 'LoveSkin'</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1276,12 +1276,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Font family and size match artwork field specification.</t>
+          <t>Field is present on the layout.</t>
         </is>
       </c>
     </row>
@@ -1293,32 +1293,32 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Color Name (Placement)</t>
+          <t>Size (max 12 digits) (Font)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Inside safe print zone</t>
+          <t>Arial 5.0pt</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>X: 2.0mm, Y: 23.03mm (W:17.02mm, H:2.52mm)</t>
+          <t>Helvetica-Bold 8.0pt</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Coordinates are within approved tolerance.</t>
+          <t>Size mismatch (8.0pt vs expected 5.0pt)</t>
         </is>
       </c>
     </row>
@@ -1330,17 +1330,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>RPO Number</t>
+          <t>Size (max 12 digits) (Placement)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Present</t>
+          <t>Inside safe print zone</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Found: 'RPO: 1000341139'</t>
+          <t>X: 3.0mm, Y: 5.98mm (W:12.55mm, H:3.89mm)</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1355,7 +1355,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Field is present on the layout.</t>
+          <t>Coordinates are within approved tolerance.</t>
         </is>
       </c>
     </row>
@@ -1367,17 +1367,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>RPO Number (Font)</t>
+          <t>Article number (12 digits)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Helvetica 5.2pt</t>
+          <t>Present</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Helvetica 5.2pt</t>
+          <t>Found: 'Articolo / Article: Z5E213TS'</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Font family and size match artwork field specification.</t>
+          <t>Field is present on the layout.</t>
         </is>
       </c>
     </row>
@@ -1404,17 +1404,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>RPO Number (Placement)</t>
+          <t>Article number (12 digits) (Font)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Inside safe print zone</t>
+          <t>Arial 5.0pt</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>X: 2.0mm, Y: 27.03mm (W:15.19mm, H:2.52mm)</t>
+          <t>Helvetica 5.0pt</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1424,12 +1424,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Coordinates are within approved tolerance.</t>
+          <t>Font family and size match artwork field specification.</t>
         </is>
       </c>
     </row>
@@ -1441,17 +1441,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SKU Sequence</t>
+          <t>Article number (12 digits) (Placement)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Present</t>
+          <t>Inside safe print zone</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Found: 'SKU: 1/3'</t>
+          <t>X: 3.0mm, Y: 15.6mm (W:21.66mm, H:2.42mm)</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Field is present on the layout.</t>
+          <t>Coordinates are within approved tolerance.</t>
         </is>
       </c>
     </row>
@@ -1478,17 +1478,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SKU Sequence (Font)</t>
+          <t>Color (15 digits)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Helvetica 5.2pt</t>
+          <t>Present</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Helvetica 5.2pt</t>
+          <t>Found: 'Colore / Color: Nero'</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Font family and size match artwork field specification.</t>
+          <t>Field is present on the layout.</t>
         </is>
       </c>
     </row>
@@ -1515,17 +1515,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SKU Sequence (Placement)</t>
+          <t>Color (15 digits) (Font)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Inside safe print zone</t>
+          <t>Arial 5.0pt</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>X: 2.0mm, Y: 31.03mm (W:7.34mm, H:2.52mm)</t>
+          <t>Helvetica 5.0pt</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1535,12 +1535,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Coordinates are within approved tolerance.</t>
+          <t>Font family and size match artwork field specification.</t>
         </is>
       </c>
     </row>
@@ -1552,17 +1552,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Order QTY</t>
+          <t>Color (15 digits) (Placement)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Present</t>
+          <t>Inside safe print zone</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Found: 'QTY: 5'</t>
+          <t>X: 3.0mm, Y: 19.1mm (W:15.68mm, H:2.42mm)</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1577,7 +1577,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Field is present on the layout.</t>
+          <t>Coordinates are within approved tolerance.</t>
         </is>
       </c>
     </row>
@@ -1589,17 +1589,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Order QTY (Font)</t>
+          <t>QR Code Text</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Helvetica 5.2pt</t>
+          <t>Present</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Helvetica 5.2pt</t>
+          <t>Found: 'QR CODE'</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1609,12 +1609,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Font family and size match artwork field specification.</t>
+          <t>Field is present on the layout.</t>
         </is>
       </c>
     </row>
@@ -1626,17 +1626,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Order QTY (Placement)</t>
+          <t>QR Code Text (Font)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Inside safe print zone</t>
+          <t>Arial 5.0pt</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>X: 2.0mm, Y: 35.03mm (W:5.81mm, H:2.52mm)</t>
+          <t>Helvetica-Bold 4.5pt</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1646,34 +1646,34 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Coordinates are within approved tolerance.</t>
+          <t>Font family and size match artwork field specification.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Variable Data &amp; Mapping QC</t>
+          <t>Static Artwork QC</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Article</t>
+          <t>QR Code Text (Placement)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>1000341139-PT</t>
+          <t>Inside safe print zone</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1000341139-PT</t>
+          <t>X: 41.8mm, Y: 4.3mm (W:7.41mm, H:2.19mm)</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1688,29 +1688,29 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Value matches order record exactly (Record #1).</t>
+          <t>Coordinates are within approved tolerance.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Variable Data &amp; Mapping QC</t>
+          <t>Static Artwork QC</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Size</t>
+          <t>QR Code (15 x15mm)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>Present</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>Found: 'QR CODE'</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1725,29 +1725,29 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Value matches order record exactly (Record #1).</t>
+          <t>Field is present on the layout.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Variable Data &amp; Mapping QC</t>
+          <t>Static Artwork QC</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Color</t>
+          <t>QR Code (15 x15mm) (Placement)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Midnight Navy</t>
+          <t>Inside safe print zone</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Midnight Navy</t>
+          <t>X: 41.8mm, Y: 4.3mm (W:7.41mm, H:2.19mm)</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1762,7 +1762,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Value matches order record exactly (Record #1).</t>
+          <t>Coordinates are within approved tolerance.</t>
         </is>
       </c>
     </row>
@@ -1774,17 +1774,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>RPO</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1000341139</t>
+          <t>Z5E213TS</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1000341139</t>
+          <t>Z5E213TS</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1811,17 +1811,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>SKU</t>
+          <t>Size</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1/3</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1/3</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1848,17 +1848,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>QTY</t>
+          <t>Color</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>Nero</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>Nero</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">

--- a/sample_data/test_output_audit.xlsx
+++ b/sample_data/test_output_audit.xlsx
@@ -440,7 +440,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-16 23:37:49</t>
+          <t>2026-08-16 23:49:26</t>
         </is>
       </c>
     </row>
